--- a/diseases/d156/2026-2029.xlsx
+++ b/diseases/d156/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,97 +716,126 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>44</v>
       </c>
-      <c r="N2" t="n">
-        <v>9.935483870967742</v>
-      </c>
       <c r="O2" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.8321546052476049</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -690,97 +864,126 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>42</v>
       </c>
-      <c r="N3" t="n">
-        <v>9.483870967741934</v>
-      </c>
       <c r="O3" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.7943293959181681</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -809,97 +1012,126 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>48</v>
       </c>
-      <c r="N4" t="n">
-        <v>12</v>
-      </c>
       <c r="O4" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.9078050239064779</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -928,97 +1160,126 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>33</v>
       </c>
-      <c r="N5" t="n">
-        <v>7.451612903225806</v>
-      </c>
       <c r="O5" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.6241159539357036</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1047,97 +1308,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>27</v>
       </c>
-      <c r="N6" t="n">
-        <v>6.3</v>
-      </c>
       <c r="O6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.5106403259473938</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1166,97 +1456,126 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>35</v>
       </c>
-      <c r="N7" t="n">
-        <v>7.903225806451614</v>
-      </c>
       <c r="O7" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.6619411632651402</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1374,7 +1693,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1384,27 +1703,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>229</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1414,22 +1733,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d156/2026-2029.xlsx
+++ b/diseases/d156/2026-2029.xlsx
@@ -776,28 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -864,7 +878,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -899,53 +913,139 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.7943293959181681</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1047,53 +1147,67 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="O4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9078050239064779</v>
+        <v>0.7943293959181681</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1160,7 +1274,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1195,53 +1309,139 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6241159539357036</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1343,53 +1543,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5106403259473938</v>
+        <v>0.9078050239064779</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1456,126 +1670,1400 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>48</v>
+      </c>
+      <c r="O7" t="n">
+        <v>48</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>D156</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Gastroenteritis</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>胃肠炎</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6241159539357036</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>33</v>
+      </c>
+      <c r="O9" t="n">
+        <v>33</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5106403259473938</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>27</v>
+      </c>
+      <c r="O11" t="n">
+        <v>27</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N12" t="n">
         <v>35</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O12" t="n">
         <v>35</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R12" t="n">
         <v>0.6619411632651402</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>35</v>
+      </c>
+      <c r="O13" t="n">
+        <v>35</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1707,7 +3195,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1727,7 +3215,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1737,7 +3225,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d156/2026-2029.xlsx
+++ b/diseases/d156/2026-2029.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1953,9 +1953,6 @@
       <c r="O8" t="n">
         <v>33</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.6241159539357036</v>
       </c>
@@ -2202,7 +2199,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2349,9 +2346,6 @@
       <c r="O10" t="n">
         <v>27</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.5106403259473938</v>
       </c>
@@ -2598,7 +2592,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2745,9 +2739,6 @@
       <c r="O12" t="n">
         <v>35</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.6619411632651402</v>
       </c>
@@ -2994,7 +2985,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">

--- a/diseases/d156/2026-2029.xlsx
+++ b/diseases/d156/2026-2029.xlsx
@@ -3060,6 +3060,399 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>36</v>
+      </c>
+      <c r="O14" t="n">
+        <v>36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6808537679298584</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gastroenteritis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D156</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>胃肠炎</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>36</v>
+      </c>
+      <c r="O15" t="n">
+        <v>36</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly source-defined gastroenteritis notifications.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_NZ_GASTROENTERITIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3093,7 +3486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3186,7 +3579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -3206,7 +3599,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3238,7 +3631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>229</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16">
